--- a/output/2024-01-15_测试科技有限公司.xlsx
+++ b/output/2024-01-15_测试科技有限公司.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,12 +115,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.125" customWidth="1" min="1" max="1"/>
@@ -504,7 +498,7 @@
     <row r="1" ht="27" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>测试公司-下场单</t>
+          <t>测试公司</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -548,7 +542,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>单位地址：北京市朝阳区测试路123号</t>
+          <t>单位地址：北京市朝阳区</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -558,7 +552,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>下场人员：张三、李四、王五</t>
+          <t>下场人员：张三、李四</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -570,17 +564,17 @@
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>委托单备注：请尽快完成检定</t>
+          <t>委托单备注：测试</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>设备总数：2</t>
+          <t>设备总数：1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>带回数量：1</t>
+          <t>带回数量：0</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -672,57 +666,12 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>精度1.6级，0-1.6MPa</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
           <t>张三</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>数字万用表</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Fluke 17B</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>FL202402001</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>EQ-002</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>福禄克</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>带回校准</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>李四</t>
         </is>
       </c>
     </row>
